--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92566796408</v>
+        <v>46157.93093838932</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93093838932</v>
+        <v>46157.9317077963</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9317077963</v>
+        <v>46157.93398621389</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93398621389</v>
+        <v>46157.93716358845</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93716358845</v>
+        <v>46158.28214971014</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28214971014</v>
+        <v>46158.29676450006</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29676450006</v>
+        <v>46158.29813069537</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29813069537</v>
+        <v>46158.33385937839</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33385937839</v>
+        <v>46158.36855714646</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36855714646</v>
+        <v>46158.37286425178</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
